--- a/data/trans_orig/IP16A08-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP16A08-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4599</t>
+          <t>4503</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13527</t>
+          <t>13211</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1652</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8807</t>
+          <t>8892</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8030</t>
+          <t>7569</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18738</t>
+          <t>18903</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,74%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19291</t>
+          <t>19607</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28219</t>
+          <t>28315</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19867</t>
+          <t>19782</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27022</t>
+          <t>26599</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42754</t>
+          <t>42589</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53462</t>
+          <t>53923</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>87,69%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7796</t>
+          <t>8250</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9143</t>
+          <t>9259</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4741</t>
+          <t>4660</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13673</t>
+          <t>14025</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,91%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>33851</t>
+          <t>33397</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40300</t>
+          <t>39710</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32163</t>
+          <t>32047</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39329</t>
+          <t>39314</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>69279</t>
+          <t>68927</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>78211</t>
+          <t>78292</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,38%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>609</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5034</t>
+          <t>4989</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>2808</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10088</t>
+          <t>10365</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>4044</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12519</t>
+          <t>12553</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,82%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20130</t>
+          <t>20175</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24548</t>
+          <t>24555</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25035</t>
+          <t>24758</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32473</t>
+          <t>32315</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>47767</t>
+          <t>47733</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>55854</t>
+          <t>56242</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>93,29%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2407</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9945</t>
+          <t>9241</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4704</t>
+          <t>4906</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13336</t>
+          <t>13441</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8458</t>
+          <t>8913</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19717</t>
+          <t>19586</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,37%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15732</t>
+          <t>16436</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22881</t>
+          <t>23270</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25481</t>
+          <t>25376</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34113</t>
+          <t>33911</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>44777</t>
+          <t>44908</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>56036</t>
+          <t>55581</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,18%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13412</t>
+          <t>12958</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26859</t>
+          <t>26910</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17037</t>
+          <t>16676</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31549</t>
+          <t>31017</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34147</t>
+          <t>32995</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53489</t>
+          <t>52511</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,5%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>98446</t>
+          <t>98395</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>111893</t>
+          <t>112347</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>112370</t>
+          <t>112902</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>126882</t>
+          <t>127243</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>215735</t>
+          <t>216713</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>235077</t>
+          <t>236229</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,74%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3624</t>
+          <t>3895</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12198</t>
+          <t>12099</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>693</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6098</t>
+          <t>6412</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>5846</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15294</t>
+          <t>15923</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>24,17%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19248</t>
+          <t>19347</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27822</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28326</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33735</t>
+          <t>33731</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>50576</t>
+          <t>49947</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60387</t>
+          <t>60024</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,13%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7188</t>
+          <t>7251</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3955</t>
+          <t>3597</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12545</t>
+          <t>11995</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>6580</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16188</t>
+          <t>16522</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,31%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>33836</t>
+          <t>33773</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39760</t>
+          <t>39773</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27775</t>
+          <t>28325</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36365</t>
+          <t>36723</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>65156</t>
+          <t>64822</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>75520</t>
+          <t>74764</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>91,91%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1818</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8720</t>
+          <t>8670</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6932</t>
+          <t>6925</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4481</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12668</t>
+          <t>12815</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,58%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24244</t>
+          <t>24294</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>30929</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29062</t>
+          <t>29069</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>34727</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56290</t>
+          <t>56143</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>64477</t>
+          <t>64467</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,49%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>912</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6860</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3170</t>
+          <t>3438</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12321</t>
+          <t>11980</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>4832</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15615</t>
+          <t>15150</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34926</t>
+          <t>35270</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40885</t>
+          <t>40874</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34908</t>
+          <t>35249</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>44059</t>
+          <t>43791</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>73400</t>
+          <t>73865</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>83865</t>
+          <t>84183</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,57%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11969</t>
+          <t>12225</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25357</t>
+          <t>25543</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13322</t>
+          <t>14124</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27433</t>
+          <t>28594</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28536</t>
+          <t>28961</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47421</t>
+          <t>47480</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,56%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>121864</t>
+          <t>121678</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>135252</t>
+          <t>134996</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>130533</t>
+          <t>129372</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>144644</t>
+          <t>143842</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>257766</t>
+          <t>257707</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>276651</t>
+          <t>276226</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,51%</t>
         </is>
       </c>
     </row>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5937</t>
+          <t>6290</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11170</t>
+          <t>11875</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4630</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14066</t>
+          <t>14462</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,8%</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18422</t>
+          <t>18069</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13006</t>
+          <t>12301</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20494</t>
+          <t>20360</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34470</t>
+          <t>34074</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43906</t>
+          <t>43856</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,36%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2639</t>
+          <t>2554</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9943</t>
+          <t>9412</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8780</t>
+          <t>8543</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6411</t>
+          <t>6333</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16161</t>
+          <t>16396</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,55%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32756</t>
+          <t>33287</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40060</t>
+          <t>40145</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32367</t>
+          <t>32604</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39158</t>
+          <t>39163</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>67685</t>
+          <t>67450</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>77435</t>
+          <t>77513</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,45%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>573</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>564</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6188</t>
+          <t>5696</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1594</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8467</t>
+          <t>8371</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22453</t>
+          <t>22689</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27048</t>
+          <t>27042</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21618</t>
+          <t>22110</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27207</t>
+          <t>27242</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>46954</t>
+          <t>47050</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>53992</t>
+          <t>53827</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t>4449</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12844</t>
+          <t>13482</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1501</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8630</t>
+          <t>8522</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7796</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18682</t>
+          <t>18267</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,03%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19944</t>
+          <t>19306</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28337</t>
+          <t>28339</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21516</t>
+          <t>21624</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28411</t>
+          <t>28645</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>44252</t>
+          <t>44667</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>55138</t>
+          <t>55760</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>88,6%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>11815</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25387</t>
+          <t>24797</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11902</t>
+          <t>12105</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25702</t>
+          <t>25464</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27028</t>
+          <t>27336</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45709</t>
+          <t>45555</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,17%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>102074</t>
+          <t>102664</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>115485</t>
+          <t>115646</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>97574</t>
+          <t>97812</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>111374</t>
+          <t>111171</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>205028</t>
+          <t>205182</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>223709</t>
+          <t>223401</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,1%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>874</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6620</t>
+          <t>6652</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4559</t>
+          <t>4705</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1652</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8991</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,03%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19221</t>
+          <t>19189</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25012</t>
+          <t>24967</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23101</t>
+          <t>22955</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44510</t>
+          <t>44391</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51565</t>
+          <t>51849</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,91%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>1426</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8656</t>
+          <t>7876</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4398</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14838</t>
+          <t>14856</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7199</t>
+          <t>7396</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19347</t>
+          <t>20445</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35586</t>
+          <t>36366</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>42839</t>
+          <t>42816</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>48971</t>
+          <t>48953</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>59411</t>
+          <t>59108</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>88704</t>
+          <t>87606</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>100852</t>
+          <t>100655</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,15%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>12610</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12572</t>
+          <t>12597</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5735</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21152</t>
+          <t>20681</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,43%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64418</t>
+          <t>64461</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>75837</t>
+          <t>75541</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44351</t>
+          <t>44326</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54252</t>
+          <t>53994</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>112842</t>
+          <t>113313</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>128259</t>
+          <t>128434</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,85%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>583</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5655</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>581</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8272</t>
+          <t>8209</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,75%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24906</t>
+          <t>25241</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29957</t>
+          <t>29978</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28626</t>
+          <t>28598</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33230</t>
+          <t>33228</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>56098</t>
+          <t>56161</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>62761</t>
+          <t>62575</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7776</t>
+          <t>7779</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23123</t>
+          <t>22522</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11853</t>
+          <t>11891</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27454</t>
+          <t>27497</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22666</t>
+          <t>23828</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45449</t>
+          <t>45074</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>154592</t>
+          <t>155193</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>169939</t>
+          <t>169936</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>154747</t>
+          <t>154704</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>170348</t>
+          <t>170310</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>314467</t>
+          <t>314842</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>337250</t>
+          <t>336088</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,38%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A08-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP16A08-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4481</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2035</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8463</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>15,63%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>29,51%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>8281</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4503</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13211</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4836</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12910</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>25,23%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>13,72%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>40,26%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4481</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2075</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8892</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>15,63%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7569</t>
+          <t>7862</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18903</t>
+          <t>18268</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>29,71%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24193</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>20211</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>26639</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>84,37%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>70,49%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>92,9%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>24537</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>19607</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>28315</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>19908</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>27982</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>74,77%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>59,74%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>86,28%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>24193</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>19782</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>26599</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>84,37%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42589</t>
+          <t>43224</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53923</t>
+          <t>53630</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,22%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>32818</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>32818</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>32818</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4603</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1903</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8473</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11,14%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,61%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>20,51%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>3942</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1937</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8250</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1345</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7833</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>9,47%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,65%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>19,81%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4603</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1992</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>9259</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>11,14%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4660</t>
+          <t>4596</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14025</t>
+          <t>13875</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>36703</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>32833</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>39403</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>88,86%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>79,49%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,39%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>37705</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>33397</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>39710</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>33814</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>40302</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>90,53%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>80,19%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,35%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>36703</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>32047</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>39314</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>88,86%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>68927</t>
+          <t>69077</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>78292</t>
+          <t>78356</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,46%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>41647</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5861</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2651</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9929</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>16,69%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7,55%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>28,27%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1885</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>609</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4989</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5153</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>7,49%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>19,83%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5861</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2808</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>10365</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>16,69%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4044</t>
+          <t>4380</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12553</t>
+          <t>12905</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>21,41%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>29262</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>25194</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>32472</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>83,31%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>71,73%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>92,45%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>23279</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>20175</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>24555</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>20011</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>24549</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>92,51%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>80,17%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,58%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>29262</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>24758</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>32315</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>83,31%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>47733</t>
+          <t>47381</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>56242</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>92,73%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>25164</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>25164</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>25164</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8466</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4520</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>13005</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>21,81%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>11,64%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>33,5%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>5258</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2407</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>9241</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2229</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>9306</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>20,48%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9,38%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>35,99%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>8466</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>4906</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>13441</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>21,81%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8913</t>
+          <t>8844</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19586</t>
+          <t>19566</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,34%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>30351</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>25812</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>34297</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>78,19%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>66,5%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>88,36%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>20419</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>16436</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>23270</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>16371</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>23448</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>79,52%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>64,01%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>90,62%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>30351</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>25376</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>33911</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>78,19%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>44908</t>
+          <t>44928</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>55581</t>
+          <t>55650</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,29%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>25677</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>25677</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>25677</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>23411</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>16713</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>30782</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>16,27%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>11,61%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>21,39%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>19366</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>12958</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>26910</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>13711</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>27978</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>15,45%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>10,34%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>21,48%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>23411</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>16676</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>31017</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>16,27%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32995</t>
+          <t>34029</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52511</t>
+          <t>53746</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>120508</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>113137</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>127206</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>83,73%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>78,61%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>88,39%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>105939</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>98395</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>112347</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>97327</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>111594</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>84,55%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>78,52%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>89,66%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>120508</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>112902</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>127243</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>83,73%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>216713</t>
+          <t>215478</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>236229</t>
+          <t>235195</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,36%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2736</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>681</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6314</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7,95%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>18,34%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>7144</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3895</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12099</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3501</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12225</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>22,72%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12,39%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>38,48%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2736</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>693</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6412</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,95%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>5643</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15923</t>
+          <t>15455</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>31688</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>28110</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>33743</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>92,05%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>81,66%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,02%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>24302</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>19347</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>27551</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>19221</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>27945</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>77,28%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>61,52%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>87,61%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>31688</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>28012</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>33731</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>92,05%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49947</t>
+          <t>50415</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60024</t>
+          <t>60227</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,43%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>34424</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>34424</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>34424</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>31446</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>31446</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>31446</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>34424</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>34424</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>34424</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7419</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3687</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11909</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>18,4%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>9,14%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>29,54%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>3261</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1251</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7251</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1264</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6709</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>7,95%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>17,68%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>7419</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>3597</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>11995</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>18,4%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6580</t>
+          <t>6281</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16522</t>
+          <t>16772</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>32901</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>28411</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>81,6%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>70,46%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>90,86%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>37763</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>33773</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>39773</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>34315</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>39760</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>92,05%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>82,32%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,95%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>32901</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>28325</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>36723</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>81,6%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>64822</t>
+          <t>64572</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>74764</t>
+          <t>75063</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>92,28%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>40320</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>40320</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>40320</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>41024</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>41024</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>41024</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>40320</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>40320</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>40320</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3423</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7371</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9,51%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,03%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>20,48%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4567</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2035</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8670</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2069</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8717</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>13,85%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,17%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>26,3%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3423</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1267</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6925</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,51%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4491</t>
+          <t>4278</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12815</t>
+          <t>12743</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,48%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>32571</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>28623</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>34545</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>90,49%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>79,52%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,97%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>28397</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>24294</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>30929</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>24247</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>30895</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>86,15%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>73,7%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>93,83%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>32571</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>29069</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>34727</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>90,49%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56143</t>
+          <t>56215</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>64467</t>
+          <t>64680</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,8%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35994</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35994</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35994</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>32964</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>32964</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>32964</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>35994</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>35994</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>35994</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6466</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3236</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12175</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13,69%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6,85%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>25,78%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2786</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>912</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6516</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6528</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>6,67%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15,59%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>6466</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3438</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>11980</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>13,69%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4832</t>
+          <t>4821</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15150</t>
+          <t>15458</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,37%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>40763</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>35054</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>43993</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>86,31%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>74,22%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>93,15%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>39000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>35270</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>40874</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>35258</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>41163</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>93,33%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>84,41%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,82%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>40763</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>35249</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>43791</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>86,31%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>73865</t>
+          <t>73557</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>84183</t>
+          <t>84194</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,58%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>47229</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>47229</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>47229</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>41786</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>41786</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>41786</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>47229</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>47229</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>47229</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>20044</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>13676</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>27640</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>12,69%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>8,66%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>17,5%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>17758</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>12225</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>25543</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>11906</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>25693</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>12,06%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8,3%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>17,35%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>20044</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>14124</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>28594</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>12,69%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28961</t>
+          <t>28283</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47480</t>
+          <t>49257</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>137922</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>130326</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>144290</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>87,31%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>82,5%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>91,34%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>129463</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>121678</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>134996</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>121528</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>135315</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>87,94%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>82,65%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>91,7%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>137922</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>129372</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>143842</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>87,31%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>257707</t>
+          <t>255930</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>276226</t>
+          <t>276904</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,73%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>147221</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>147221</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>147221</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6994</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3775</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11726</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>28,93%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>15,62%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>48,5%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1782</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6290</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5674</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>7,31%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>25,82%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6994</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3816</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>11875</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>28,93%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>15,78%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>4672</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14462</t>
+          <t>13818</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>28,47%</t>
         </is>
       </c>
     </row>
@@ -4730,74 +4730,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17182</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12450</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>20401</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>71,07%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>51,5%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>84,38%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>22577</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>18069</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>18685</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>24359</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>92,69%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>74,18%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>76,71%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>17182</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>12301</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>20360</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>71,07%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>50,88%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>84,22%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>54</t>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34074</t>
+          <t>34718</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43856</t>
+          <t>43864</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,38%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24176</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24176</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24176</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>24359</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>24359</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>24359</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>24176</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>24176</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>24176</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4660</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8851</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11,33%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,82%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>21,51%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>5745</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2554</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9412</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2726</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>10043</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>13,46%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,98%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>22,04%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4660</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1984</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8543</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>11,33%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>6524</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16396</t>
+          <t>16029</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,12%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>36487</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>32296</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>39163</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>88,67%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>78,49%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,18%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>36954</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>33287</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>40145</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>32656</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>39973</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>86,54%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>77,96%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,02%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>36487</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>32604</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>39163</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>88,67%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>67450</t>
+          <t>67817</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>77513</t>
+          <t>77322</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,22%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>41147</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>41147</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>41147</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>42699</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>42699</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>42699</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>41147</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>41147</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>41147</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2214</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5989</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7,96%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>21,54%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1885</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>573</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4926</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5082</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>6,83%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>17,84%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2214</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>564</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5696</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>7,96%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1594</t>
+          <t>1546</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8371</t>
+          <t>8428</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,21%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>25592</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>21817</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>27216</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>92,04%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>78,46%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,88%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>25730</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>22689</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>27042</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>22533</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>27047</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>93,17%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>82,16%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,92%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>25592</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>22110</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>27242</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>92,04%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>47050</t>
+          <t>46993</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>53827</t>
+          <t>53875</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>27806</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>27806</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>27806</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>27615</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>27615</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>27615</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>27806</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>27806</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>27806</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4407</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8462</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>14,62%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6,77%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>28,07%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>8211</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4449</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>13482</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4214</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>13399</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>25,04%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>13,57%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>41,12%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4407</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1501</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8522</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>14,62%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>7514</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18267</t>
+          <t>18960</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>30,13%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>25739</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>21684</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>28106</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>85,38%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>71,93%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>93,23%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>24577</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>19306</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>28339</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>19389</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>28574</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>74,96%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>58,88%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>86,43%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>25739</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>21624</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>28645</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>85,38%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>44667</t>
+          <t>43974</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>55760</t>
+          <t>55420</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,06%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>30146</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>30146</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>30146</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>32788</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>32788</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>32788</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>30146</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>30146</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>30146</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>18275</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>12814</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>25905</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>14,82%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>10,39%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>21,01%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>17623</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>11815</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>24797</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>12002</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>25156</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>13,83%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>9,27%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>19,45%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>18275</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>12105</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>25464</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>14,82%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27336</t>
+          <t>27656</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45555</t>
+          <t>49384</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>19,7%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>105001</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>97371</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>110462</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>85,18%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>78,99%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>89,61%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>109838</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>102664</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>115646</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>102305</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>115459</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>86,17%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>80,55%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>90,73%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>105001</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>97812</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>111171</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>85,18%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>205182</t>
+          <t>201353</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>223401</t>
+          <t>223081</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>88,97%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1319</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3909</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,36%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>15,87%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3036</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>874</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6652</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,75%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>25,74%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>925</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4705</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4418</t>
+          <t>4533</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1652</t>
+          <t>1873</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>8651</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,99%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>23303</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>20713</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24622</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>94,64%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>84,13%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>22805</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>19189</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>24967</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>88,25%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>74,26%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,62%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26277</t>
+          <t>23093</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22955</t>
+          <t>19015</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27660</t>
+          <t>25383</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>49083</t>
+          <t>46396</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44391</t>
+          <t>42278</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51849</t>
+          <t>49056</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,32%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24622</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24622</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24622</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>25841</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>25841</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>25841</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>27660</t>
+          <t>26308</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27660</t>
+          <t>26308</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27660</t>
+          <t>26308</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>53501</t>
+          <t>50929</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>53501</t>
+          <t>50929</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>53501</t>
+          <t>50929</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7850</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4028</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>12989</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>13,9%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,13%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>23,01%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>3724</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1426</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7876</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>8,42%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,22%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>17,8%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8837</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4701</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14856</t>
+          <t>8063</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>12561</t>
+          <t>11667</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7396</t>
+          <t>7064</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20445</t>
+          <t>18474</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,95%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>48608</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>43469</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>52430</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>86,1%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>76,99%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>92,87%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>40518</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>36366</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>42816</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>91,58%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>82,2%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,78%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>54972</t>
+          <t>32320</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>48953</t>
+          <t>28073</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>59108</t>
+          <t>34680</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>95490</t>
+          <t>80927</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>87606</t>
+          <t>74120</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>100655</t>
+          <t>85530</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>92,37%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>56458</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>56458</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>56458</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>44242</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>44242</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>44242</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>63809</t>
+          <t>36136</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>63809</t>
+          <t>36136</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>63809</t>
+          <t>36136</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>108051</t>
+          <t>92594</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>108051</t>
+          <t>92594</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>108051</t>
+          <t>92594</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6082</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1530</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12610</t>
+          <t>12787</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6455</t>
+          <t>6344</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>2967</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12597</t>
+          <t>11960</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>12537</t>
+          <t>12503</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>6970</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20681</t>
+          <t>20441</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>46196</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>39568</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>49423</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>88,24%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>75,58%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>94,4%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>70989</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>64461</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>75541</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>92,11%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>83,64%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,01%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>50468</t>
+          <t>44482</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44326</t>
+          <t>38866</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53994</t>
+          <t>47859</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>121457</t>
+          <t>90678</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>113313</t>
+          <t>82740</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>128434</t>
+          <t>96211</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>93,24%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>52355</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>52355</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>52355</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>77071</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>77071</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>77071</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>56923</t>
+          <t>50826</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>56923</t>
+          <t>50826</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>56923</t>
+          <t>50826</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>133994</t>
+          <t>103181</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>133994</t>
+          <t>103181</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>133994</t>
+          <t>103181</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>505</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1935</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>531</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>5614</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4080</t>
+          <t>3872</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>1593</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8209</t>
+          <t>7970</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>13,01%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>29762</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>26647</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>31012</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>94,43%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>84,55%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,4%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>28416</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>25241</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>29978</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>92,98%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>82,59%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,09%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>31874</t>
+          <t>27606</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28598</t>
+          <t>24109</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33228</t>
+          <t>29192</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>60290</t>
+          <t>57368</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>56161</t>
+          <t>53270</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>62575</t>
+          <t>59647</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>31517</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>31517</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>31517</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>30561</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>30561</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>30561</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>64370</t>
+          <t>61240</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>64370</t>
+          <t>61240</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>64370</t>
+          <t>61240</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>17083</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>11064</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>25466</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>10,36%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>6,71%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>15,44%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>14986</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>7779</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>22522</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>8,43%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,38%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,67%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>18609</t>
+          <t>15492</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11891</t>
+          <t>9733</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27497</t>
+          <t>23447</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>33595</t>
+          <t>32574</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23828</t>
+          <t>23936</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45074</t>
+          <t>42490</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>147869</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>139486</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>153888</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>89,64%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>84,56%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>93,29%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>162729</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>155193</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>169936</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>91,57%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>87,33%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>95,62%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>163592</t>
+          <t>127500</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>154704</t>
+          <t>119545</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>170310</t>
+          <t>133259</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>326321</t>
+          <t>275370</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>314842</t>
+          <t>265454</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>336088</t>
+          <t>284008</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>92,23%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
